--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -705,11 +705,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1980,11 +1980,11 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2133,11 +2133,11 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2286,11 +2286,11 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2439,11 +2439,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2541,11 +2541,11 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2694,11 +2694,11 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2745,11 +2745,11 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2847,11 +2847,11 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2898,11 +2898,11 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2949,11 +2949,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3051,11 +3051,11 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3102,11 +3102,11 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3204,11 +3204,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3306,11 +3306,11 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3612,11 +3612,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -603,11 +603,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -654,11 +654,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1164,11 +1164,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1317,11 +1317,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1368,11 +1368,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,11 +1419,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1470,11 +1470,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1623,11 +1623,11 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1725,11 +1725,11 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1776,11 +1776,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1827,11 +1827,11 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2031,11 +2031,11 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2082,11 +2082,11 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2388,11 +2388,11 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2592,11 +2592,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2643,11 +2643,11 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3000,11 +3000,11 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3357,11 +3357,11 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3714,11 +3714,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,12 +2312,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Petroleo WTI</t>
+          <t>RET Bova11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RET Bova11</t>
+          <t>RET DOW Jones</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2402,24 +2402,24 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
+          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RET DOW Jones</t>
+          <t>RET Dolar REAL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2453,24 +2453,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
+          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RET Dolar REAL</t>
+          <t>RET EURO REAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2504,24 +2504,24 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
+          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RET EURO REAL</t>
+          <t>RET Ibovespa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2555,24 +2555,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
+          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RET Ibovespa</t>
+          <t>RET Ivvb11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2606,24 +2606,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
+          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RET Ivvb11</t>
+          <t>RET Milho</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2657,24 +2657,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
+          <t>data/final/dashboard/yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RET Milho</t>
+          <t>RET Nasdaq</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2708,24 +2708,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_milho.json</t>
+          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RET Nasdaq</t>
+          <t>RET OURO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2759,24 +2759,24 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
+          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RET OURO</t>
+          <t>RET Petroleo Brent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2810,24 +2810,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RET Petroleo Brent</t>
+          <t>RET Petroleo WTI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RET Petroleo WTI</t>
+          <t>RET SOJA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2912,24 +2912,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_ret_soja.json</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RET SOJA</t>
+          <t>RET Smal11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2963,24 +2963,24 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_soja.json</t>
+          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RET Smal11</t>
+          <t>RET Sp500</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3014,24 +3014,24 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
+          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RET Sp500</t>
+          <t>SOJA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3051,11 +3051,11 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3065,24 +3065,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
+          <t>data/final/dashboard/yahoo_soja.json</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SOJA</t>
+          <t>Smal11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3116,24 +3116,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_soja.json</t>
+          <t>data/final/dashboard/yahoo_smal11.json</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Smal11</t>
+          <t>Sp500</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3167,35 +3167,35 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_smal11.json</t>
+          <t>data/final/dashboard/yahoo_sp500.json</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sp500</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_sp500.json</t>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>DIF CDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3269,24 +3269,24 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIF CDI</t>
+          <t>DIF Juros Credito Total</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3315,29 +3315,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIF Juros Credito Total</t>
+          <t>DIF Selic META</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3366,29 +3366,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DIF Selic META</t>
+          <t>DIF Selic OVER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3422,24 +3422,24 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DIF Selic OVER</t>
+          <t>Juros Credito Total</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3459,38 +3459,38 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Juros Credito Total</t>
+          <t>Selic META</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3519,29 +3519,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Selic META</t>
+          <t>Selic OVER</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3575,24 +3575,24 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Selic OVER</t>
+          <t>Reservas Internacionais</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3621,29 +3621,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reservas Internacionais</t>
+          <t>VAR PCT Reservas Internacionais</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3677,61 +3677,10 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>VAR PCT Reservas Internacionais</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>59</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,12 +2312,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RET Bova11</t>
+          <t>Petroleo WTI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
+          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RET DOW Jones</t>
+          <t>RET Bova11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2402,24 +2402,24 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
+          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RET Dolar REAL</t>
+          <t>RET DOW Jones</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2453,24 +2453,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
+          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RET EURO REAL</t>
+          <t>RET Dolar REAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2504,24 +2504,24 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
+          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RET Ibovespa</t>
+          <t>RET EURO REAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2555,24 +2555,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
+          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RET Ivvb11</t>
+          <t>RET Ibovespa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2606,24 +2606,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
+          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RET Milho</t>
+          <t>RET Ivvb11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2657,24 +2657,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_milho.json</t>
+          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RET Nasdaq</t>
+          <t>RET Milho</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2708,24 +2708,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
+          <t>data/final/dashboard/yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RET OURO</t>
+          <t>RET Nasdaq</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2759,24 +2759,24 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
+          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RET Petroleo Brent</t>
+          <t>RET OURO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2810,24 +2810,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
+          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RET Petroleo WTI</t>
+          <t>RET Petroleo Brent</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RET SOJA</t>
+          <t>RET Petroleo WTI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2912,24 +2912,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_soja.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RET Smal11</t>
+          <t>RET SOJA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2963,24 +2963,24 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
+          <t>data/final/dashboard/yahoo_ret_soja.json</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RET Sp500</t>
+          <t>RET Smal11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3014,24 +3014,24 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
+          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOJA</t>
+          <t>RET Sp500</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3051,11 +3051,11 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3065,24 +3065,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_soja.json</t>
+          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Smal11</t>
+          <t>SOJA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3116,24 +3116,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_smal11.json</t>
+          <t>data/final/dashboard/yahoo_soja.json</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sp500</t>
+          <t>Smal11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3167,35 +3167,35 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_sp500.json</t>
+          <t>data/final/dashboard/yahoo_smal11.json</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Sp500</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+          <t>data/final/dashboard/yahoo_sp500.json</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DIF CDI</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3269,24 +3269,24 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIF Juros Credito Total</t>
+          <t>DIF CDI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3315,29 +3315,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIF Selic META</t>
+          <t>DIF Juros Credito Total</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3366,29 +3366,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DIF Selic OVER</t>
+          <t>DIF Selic META</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3422,24 +3422,24 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Juros Credito Total</t>
+          <t>DIF Selic OVER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3459,38 +3459,38 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Selic META</t>
+          <t>Juros Credito Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3519,29 +3519,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Selic OVER</t>
+          <t>Selic META</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3575,24 +3575,24 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reservas Internacionais</t>
+          <t>Selic OVER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3621,29 +3621,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VAR PCT Reservas Internacionais</t>
+          <t>Reservas Internacionais</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3663,24 +3663,75 @@
         </is>
       </c>
       <c r="G64" t="n">
+        <v>60</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VAR PCT Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
         <v>59</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -603,11 +603,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -654,11 +654,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -705,11 +705,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1164,11 +1164,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1317,11 +1317,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1368,11 +1368,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,11 +1419,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1470,11 +1470,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1623,11 +1623,11 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1725,11 +1725,11 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1776,11 +1776,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3306,11 +3306,11 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3357,11 +3357,11 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3612,11 +3612,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3714,11 +3714,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,23 +884,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia PF</t>
+          <t>Comexstat Comex Corrente Comercio USD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -909,49 +909,49 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_corrente_comercio_usd.json</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/comexstat_comex_corrente_comercio_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia PJ</t>
+          <t>Comexstat Comex Exportacoes FOB USD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -960,49 +960,49 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia Total</t>
+          <t>Comexstat Comex Importacoes CIF USD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_cif_usd.json</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_cif_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inadimplencia PF</t>
+          <t>Comexstat Comex Importacoes FOB USD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1062,49 +1062,49 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inadimplencia PJ</t>
+          <t>Comexstat Comex Importacoes Frete USD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1113,49 +1113,49 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_frete_usd.json</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_frete_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Inadimplencia Total</t>
+          <t>Comexstat Comex Importacoes Seguro USD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1164,49 +1164,49 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_seguro_usd.json</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saldo Credito PF</t>
+          <t>Comexstat Comex Saldo Comercial USD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1215,38 +1215,38 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_saldo_comercial_usd.json</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Saldo Credito PJ</t>
+          <t>DIF Inadimplencia PF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1280,24 +1280,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_pj.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saldo Credito Total</t>
+          <t>DIF Inadimplencia PJ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1317,11 +1317,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1331,24 +1331,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito PF</t>
+          <t>DIF Inadimplencia Total</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1382,24 +1382,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pf.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito PJ</t>
+          <t>Inadimplencia PF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1419,11 +1419,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pj.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito Total</t>
+          <t>Inadimplencia PJ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1470,11 +1470,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1484,24 +1484,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_total.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IGP M</t>
+          <t>Inadimplencia Total</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1530,29 +1530,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_igp_m.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IGP M ACUM 12M</t>
+          <t>Saldo Credito PF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1572,38 +1572,38 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_igp_m_acum_12m.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INPC</t>
+          <t>Saldo Credito PJ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1637,24 +1637,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inpc.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INPC ACUM 12M</t>
+          <t>Saldo Credito Total</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1688,24 +1688,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inpc_acum_12m.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IPCA</t>
+          <t>VAR PCT Saldo Credito PF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1725,11 +1725,11 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1739,24 +1739,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_ipca.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IPCA ACUM 12M</t>
+          <t>VAR PCT Saldo Credito PJ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1776,11 +1776,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1790,35 +1790,35 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_ipca_acum_12m.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bova11</t>
+          <t>VAR PCT Saldo Credito Total</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1827,49 +1827,49 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_bova11.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DOW Jones</t>
+          <t>IGP M</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1887,40 +1887,40 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_dow_jones.json</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m.json</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dolar REAL</t>
+          <t>IGP M ACUM 12M</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1929,49 +1929,49 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_dolar_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m_acum_12m.json</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EURO REAL</t>
+          <t>INPC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1989,40 +1989,40 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_euro_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_inpc.json</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ibovespa</t>
+          <t>INPC ACUM 12M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2031,49 +2031,49 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ibovespa.json</t>
+          <t>data/final/dashboard/bcb_sgs_inpc_acum_12m.json</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ivvb11</t>
+          <t>IPCA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2091,40 +2091,40 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ivvb11.json</t>
+          <t>data/final/dashboard/bcb_sgs_ipca.json</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Milho</t>
+          <t>IPCA ACUM 12M</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2133,38 +2133,38 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_milho.json</t>
+          <t>data/final/dashboard/bcb_sgs_ipca_acum_12m.json</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Bova11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2198,24 +2198,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_nasdaq.json</t>
+          <t>data/final/dashboard/yahoo_bova11.json</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OURO</t>
+          <t>DOW Jones</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2249,24 +2249,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ouro.json</t>
+          <t>data/final/dashboard/yahoo_dow_jones.json</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Petroleo Brent</t>
+          <t>Dolar REAL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2300,24 +2300,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_petroleo_brent.json</t>
+          <t>data/final/dashboard/yahoo_dolar_real.json</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Petroleo WTI</t>
+          <t>EURO REAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_euro_real.json</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RET Bova11</t>
+          <t>Ibovespa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2388,11 +2388,11 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2402,24 +2402,24 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
+          <t>data/final/dashboard/yahoo_ibovespa.json</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RET DOW Jones</t>
+          <t>Ivvb11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2439,11 +2439,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
+          <t>data/final/dashboard/yahoo_ivvb11.json</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RET Dolar REAL</t>
+          <t>Milho</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2504,24 +2504,24 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
+          <t>data/final/dashboard/yahoo_milho.json</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RET EURO REAL</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2541,11 +2541,11 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2555,24 +2555,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
+          <t>data/final/dashboard/yahoo_nasdaq.json</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RET Ibovespa</t>
+          <t>OURO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2592,11 +2592,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
+          <t>data/final/dashboard/yahoo_ouro.json</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RET Ivvb11</t>
+          <t>Petroleo Brent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2643,11 +2643,11 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2657,24 +2657,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
+          <t>data/final/dashboard/yahoo_petroleo_brent.json</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RET Milho</t>
+          <t>Petroleo WTI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2694,11 +2694,11 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2708,24 +2708,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_milho.json</t>
+          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RET Nasdaq</t>
+          <t>RET Bova11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2759,24 +2759,24 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
+          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RET OURO</t>
+          <t>RET DOW Jones</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2810,24 +2810,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
+          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RET Petroleo Brent</t>
+          <t>RET Dolar REAL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
+          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RET Petroleo WTI</t>
+          <t>RET EURO REAL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2912,24 +2912,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RET SOJA</t>
+          <t>RET Ibovespa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2963,24 +2963,24 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_soja.json</t>
+          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RET Smal11</t>
+          <t>RET Ivvb11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3014,24 +3014,24 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
+          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RET Sp500</t>
+          <t>RET Milho</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3065,24 +3065,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
+          <t>data/final/dashboard/yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SOJA</t>
+          <t>RET Nasdaq</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3102,11 +3102,11 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3116,24 +3116,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_soja.json</t>
+          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Smal11</t>
+          <t>RET OURO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3167,24 +3167,24 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_smal11.json</t>
+          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sp500</t>
+          <t>RET Petroleo Brent</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3204,11 +3204,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3218,35 +3218,35 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_sp500.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>RET Petroleo WTI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3269,35 +3269,35 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIF CDI</t>
+          <t>RET SOJA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3320,35 +3320,35 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+          <t>data/final/dashboard/yahoo_ret_soja.json</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIF Juros Credito Total</t>
+          <t>RET Smal11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3366,40 +3366,40 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DIF Selic META</t>
+          <t>RET Sp500</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3422,35 +3422,35 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DIF Selic OVER</t>
+          <t>SOJA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3473,35 +3473,35 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+          <t>data/final/dashboard/yahoo_soja.json</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Juros Credito Total</t>
+          <t>Smal11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3519,40 +3519,40 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+          <t>data/final/dashboard/yahoo_smal11.json</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Selic META</t>
+          <t>Sp500</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3575,35 +3575,35 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+          <t>data/final/dashboard/yahoo_sp500.json</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Selic OVER</t>
+          <t>Comexstat Comex Exportacoes KG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3612,49 +3612,49 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+          <t>data/final/dashboard/comexstat_comex_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reservas Internacionais</t>
+          <t>Comexstat Comex Importacoes KG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3663,38 +3663,38 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>1997-01-31</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VAR PCT Reservas Internacionais</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -3705,33 +3705,492 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>61</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DIF CDI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>60</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DIF Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>58</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DIF Selic META</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>60</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>DIF Selic OVER</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>60</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>59</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Selic META</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>61</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Selic OVER</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>61</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>59</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VAR PCT Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
         <v>58</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2021-10-31</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1164,11 +1164,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1190,15 +1190,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Comexstat Comex Saldo Comercial USD</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Comexstat Comex NCM Acucares CANA Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>17011400</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -1215,11 +1219,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1229,35 +1233,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_saldo_comercial_usd.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia PF</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Comexstat Comex NCM Acucares CANA Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17011400</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1266,49 +1274,53 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia PJ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>09011110</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,49 +1329,53 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIF Inadimplencia Total</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>09011110</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1368,11 +1384,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1382,35 +1398,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inadimplencia PF</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1419,49 +1439,53 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inadimplencia PJ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1470,49 +1494,53 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inadimplencia Total</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1521,49 +1549,53 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inadimplencia_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saldo Credito PF</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1572,49 +1604,53 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Saldo Credito PJ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Comexstat Comex NCM FUEL OIL Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1623,49 +1659,53 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Saldo Credito Total</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Comexstat Comex NCM FUEL OIL Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1674,11 +1714,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1688,35 +1728,39 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_saldo_credito_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito PF</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Comexstat Comex NCM Milho EM GRAO Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1725,49 +1769,53 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pf.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito PJ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Comexstat Comex NCM Milho EM GRAO Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1776,49 +1824,53 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pj.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VAR PCT Saldo Credito Total</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1827,49 +1879,53 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IGP M</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1878,11 +1934,11 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1892,35 +1948,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_igp_m.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IGP M ACUM 12M</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1929,11 +1989,11 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1943,35 +2003,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_igp_m_acum_12m.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INPC</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1980,49 +2044,53 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inpc.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INPC ACUM 12M</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2031,49 +2099,53 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_inpc_acum_12m.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IPCA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2082,49 +2154,53 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-02-29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_ipca.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IPCA ACUM 12M</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Exportacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2133,49 +2209,53 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_ipca_acum_12m.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bova11</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Importacoes FOB USD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2184,49 +2264,49 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_bova11.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.json</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DOW Jones</t>
+          <t>Comexstat Comex Saldo Comercial USD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2235,49 +2315,49 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_dow_jones.json</t>
+          <t>data/final/dashboard/comexstat_comex_saldo_comercial_usd.json</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dolar REAL</t>
+          <t>DIF Inadimplencia PF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2286,49 +2366,49 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_dolar_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EURO REAL</t>
+          <t>DIF Inadimplencia PJ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2337,49 +2417,49 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_euro_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ibovespa</t>
+          <t>DIF Inadimplencia Total</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2388,49 +2468,49 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ibovespa.json</t>
+          <t>data/final/dashboard/bcb_sgs_dif_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ivvb11</t>
+          <t>Inadimplencia PF</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2439,7 +2519,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2448,40 +2528,40 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ivvb11.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pf.json</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Milho</t>
+          <t>Inadimplencia PJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2490,7 +2570,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2499,40 +2579,40 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_milho.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_pj.json</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Inadimplencia Total</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2541,7 +2621,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2550,40 +2630,40 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_nasdaq.json</t>
+          <t>data/final/dashboard/bcb_sgs_inadimplencia_total.json</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OURO</t>
+          <t>Saldo Credito PF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2592,7 +2672,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2601,40 +2681,40 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ouro.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Petroleo Brent</t>
+          <t>Saldo Credito PJ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2643,7 +2723,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2652,40 +2732,40 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_petroleo_brent.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Petroleo WTI</t>
+          <t>Saldo Credito Total</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2694,7 +2774,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2703,40 +2783,40 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
+          <t>data/final/dashboard/bcb_sgs_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RET Bova11</t>
+          <t>VAR PCT Saldo Credito PF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2745,7 +2825,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2754,40 +2834,40 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pf.json</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RET DOW Jones</t>
+          <t>VAR PCT Saldo Credito PJ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2796,7 +2876,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2805,40 +2885,40 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_pj.json</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RET Dolar REAL</t>
+          <t>VAR PCT Saldo Credito Total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2847,7 +2927,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2856,40 +2936,40 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_var_pct_saldo_credito_total.json</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RET EURO REAL</t>
+          <t>IGP M</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2902,45 +2982,45 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m.json</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RET Ibovespa</t>
+          <t>IGP M ACUM 12M</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2949,49 +3029,49 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
+          <t>data/final/dashboard/bcb_sgs_igp_m_acum_12m.json</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RET Ivvb11</t>
+          <t>INPC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3000,49 +3080,49 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
+          <t>data/final/dashboard/bcb_sgs_inpc.json</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RET Milho</t>
+          <t>INPC ACUM 12M</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3051,49 +3131,49 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_milho.json</t>
+          <t>data/final/dashboard/bcb_sgs_inpc_acum_12m.json</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RET Nasdaq</t>
+          <t>IPCA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3102,49 +3182,49 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
+          <t>data/final/dashboard/bcb_sgs_ipca.json</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RET OURO</t>
+          <t>IPCA ACUM 12M</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3153,38 +3233,38 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
+          <t>data/final/dashboard/bcb_sgs_ipca_acum_12m.json</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RET Petroleo Brent</t>
+          <t>Bova11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3204,11 +3284,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3218,24 +3298,24 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
+          <t>data/final/dashboard/yahoo_bova11.json</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RET Petroleo WTI</t>
+          <t>DOW Jones</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3255,11 +3335,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3269,24 +3349,24 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
+          <t>data/final/dashboard/yahoo_dow_jones.json</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RET SOJA</t>
+          <t>Dolar REAL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3306,11 +3386,11 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3320,24 +3400,24 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_soja.json</t>
+          <t>data/final/dashboard/yahoo_dolar_real.json</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RET Smal11</t>
+          <t>EURO REAL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3357,11 +3437,11 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3371,24 +3451,24 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
+          <t>data/final/dashboard/yahoo_euro_real.json</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RET Sp500</t>
+          <t>Ibovespa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3408,11 +3488,11 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3422,24 +3502,24 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
+          <t>data/final/dashboard/yahoo_ibovespa.json</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SOJA</t>
+          <t>Ivvb11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3473,24 +3553,24 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_soja.json</t>
+          <t>data/final/dashboard/yahoo_ivvb11.json</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Smal11</t>
+          <t>Milho</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3524,24 +3604,24 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_smal11.json</t>
+          <t>data/final/dashboard/yahoo_milho.json</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sp500</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3575,35 +3655,35 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data/final/dashboard/yahoo_sp500.json</t>
+          <t>data/final/dashboard/yahoo_nasdaq.json</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Comexstat Comex Exportacoes KG</t>
+          <t>OURO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>consolidada</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>outros</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3612,49 +3692,49 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>356</v>
+        <v>61</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_exportacoes_kg.json</t>
+          <t>data/final/dashboard/yahoo_ouro.json</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Comexstat Comex Importacoes KG</t>
+          <t>Petroleo Brent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>consolidada</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>outros</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3663,49 +3743,49 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>356</v>
+        <v>61</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1997-01-31</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_importacoes_kg.json</t>
+          <t>data/final/dashboard/yahoo_petroleo_brent.json</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Petroleo WTI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3728,35 +3808,35 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+          <t>data/final/dashboard/yahoo_petroleo_wti.json</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DIF CDI</t>
+          <t>RET Bova11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3779,35 +3859,35 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+          <t>data/final/dashboard/yahoo_ret_bova11.json</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DIF Juros Credito Total</t>
+          <t>RET DOW Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3816,7 +3896,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3825,40 +3905,40 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+          <t>data/final/dashboard/yahoo_ret_dow_jones.json</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DIF Selic META</t>
+          <t>RET Dolar REAL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3881,35 +3961,35 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+          <t>data/final/dashboard/yahoo_ret_dolar_real.json</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DIF Selic OVER</t>
+          <t>RET EURO REAL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3932,35 +4012,35 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+          <t>data/final/dashboard/yahoo_ret_euro_real.json</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Juros Credito Total</t>
+          <t>RET Ibovespa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3969,49 +4049,49 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+          <t>data/final/dashboard/yahoo_ret_ibovespa.json</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Selic META</t>
+          <t>RET Ivvb11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4020,11 +4100,11 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4034,35 +4114,35 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+          <t>data/final/dashboard/yahoo_ret_ivvb11.json</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Selic OVER</t>
+          <t>RET Milho</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4071,11 +4151,11 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4085,35 +4165,35 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+          <t>data/final/dashboard/yahoo_ret_milho.json</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reservas Internacionais</t>
+          <t>RET Nasdaq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4122,75 +4202,2195 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+          <t>data/final/dashboard/yahoo_ret_nasdaq.json</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VAR PCT Reservas Internacionais</t>
+          <t>RET OURO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>60</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_ouro.json</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_brent</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RET Petroleo Brent</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>60</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_petroleo_brent.json</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>yahoo_ret_petroleo_wti</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RET Petroleo WTI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>60</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_petroleo_wti.json</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>yahoo_ret_soja</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RET SOJA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>60</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_soja.json</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>yahoo_ret_smal11</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RET Smal11</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>60</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_smal11.json</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>yahoo_ret_sp500</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RET Sp500</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>60</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_ret_sp500.json</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>yahoo_soja</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>61</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_soja.json</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_soja.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>yahoo_smal11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Smal11</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>61</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_smal11.json</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_smal11.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>yahoo_sp500</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sp500</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>mercado_financeiro</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>61</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/yahoo_sp500.json</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>data/final/series/yahoo_sp500.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>comexstat_comex_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Comexstat Comex Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>80</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Comexstat Comex Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>80</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Acucares CANA Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>17011400</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>80</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Acucares CANA Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>17011400</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>79</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>09011110</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>80</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>09011110</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>22</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>80</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>80</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>80</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>70</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM FUEL OIL Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>80</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM FUEL OIL Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>43</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Milho EM GRAO Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>80</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Milho EM GRAO Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>80</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>80</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>66</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>80</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>80</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>80</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>5</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2020-02-29</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>80</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>76</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>bcb_sgs</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>61</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DIF CDI</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>60</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>DIF Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>58</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DIF Selic META</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>60</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DIF Selic OVER</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>60</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>59</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Selic META</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>61</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Selic OVER</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>61</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>59</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VAR PCT Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
         <v>58</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>2021-10-31</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4687,12 +4687,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Comexstat Comex Exportacoes KG</t>
+          <t>Comexstat Acucares CANA EXP FOB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -4726,24 +4726,24 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_acucares_cana_exp_fob.json</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Comexstat Comex Importacoes KG</t>
+          <t>Comexstat Acucares CANA EXP KG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -4777,31 +4777,27 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_acucares_cana_exp_kg.json</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Acucares CANA Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>17011400</t>
-        </is>
-      </c>
+          <t>Comexstat Acucares CANA IMP FOB</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -4818,7 +4814,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4832,31 +4828,27 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_acucares_cana_imp_fob.json</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Acucares CANA Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>17011400</t>
-        </is>
-      </c>
+          <t>Comexstat Acucares CANA IMP KG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -4887,31 +4879,27 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_acucares_cana_imp_kg.json</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM CAFE NAO Torrado Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>09011110</t>
-        </is>
-      </c>
+          <t>Comexstat CAFE NAO Torrado EXP FOB</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -4942,31 +4930,27 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_cafe_nao_torrado_exp_fob.json</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM CAFE NAO Torrado Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>09011110</t>
-        </is>
-      </c>
+          <t>Comexstat CAFE NAO Torrado EXP KG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -4983,45 +4967,41 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_cafe_nao_torrado_exp_kg.json</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Carne Bovina Congelada Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>02023000</t>
-        </is>
-      </c>
+          <t>Comexstat CAFE NAO Torrado IMP FOB</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5038,45 +5018,41 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_cafe_nao_torrado_imp_fob.json</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Carne Bovina Congelada Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>02023000</t>
-        </is>
-      </c>
+          <t>Comexstat CAFE NAO Torrado IMP KG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5093,45 +5069,41 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_cafe_nao_torrado_imp_kg.json</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Celulose NAO Coniferas Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>47032900</t>
-        </is>
-      </c>
+          <t>Comexstat Carne Bovina Congelada EXP FOB</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5162,31 +5134,27 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_carne_bovina_congelada_exp_fob.json</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Celulose NAO Coniferas Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>47032900</t>
-        </is>
-      </c>
+          <t>Comexstat Carne Bovina Congelada EXP KG</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5203,7 +5171,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5217,31 +5185,27 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_carne_bovina_congelada_exp_kg.json</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM FUEL OIL Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>27101922</t>
-        </is>
-      </c>
+          <t>Comexstat Carne Bovina Congelada IMP FOB</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5272,31 +5236,27 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_carne_bovina_congelada_imp_fob.json</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM FUEL OIL Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>27101922</t>
-        </is>
-      </c>
+          <t>Comexstat Carne Bovina Congelada IMP KG</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5313,45 +5273,41 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_carne_bovina_congelada_imp_kg.json</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Milho EM GRAO Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>10059010</t>
-        </is>
-      </c>
+          <t>Comexstat Celulose NAO Coniferas EXP FOB</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5382,31 +5338,27 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_celulose_nao_coniferas_exp_fob.json</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Milho EM GRAO Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>10059010</t>
-        </is>
-      </c>
+          <t>Comexstat Celulose NAO Coniferas EXP KG</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5437,31 +5389,27 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_celulose_nao_coniferas_exp_kg.json</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>26011100</t>
-        </is>
-      </c>
+          <t>Comexstat Celulose NAO Coniferas IMP FOB</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5478,7 +5426,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5492,31 +5440,27 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_celulose_nao_coniferas_imp_fob.json</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_fob.csv</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>26011100</t>
-        </is>
-      </c>
+          <t>Comexstat Celulose NAO Coniferas IMP KG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5533,7 +5477,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5547,31 +5491,27 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_celulose_nao_coniferas_imp_kg.json</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Oleos Brutos Petroleo Exportacoes KG</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>27090010</t>
-        </is>
-      </c>
+          <t>Comexstat Comex Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5602,31 +5542,27 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Oleos Brutos Petroleo Importacoes KG</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>27090010</t>
-        </is>
-      </c>
+          <t>Comexstat Comex Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>consolidada</t>
@@ -5657,29 +5593,29 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Residuos OLEO SOJA Exportacoes KG</t>
+          <t>Comexstat Comex NCM Acucares CANA Exportacoes KG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>23040090</t>
+          <t>17011400</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5712,29 +5648,29 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM Residuos OLEO SOJA Importacoes KG</t>
+          <t>Comexstat Comex NCM Acucares CANA Importacoes KG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>23040090</t>
+          <t>17011400</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5753,11 +5689,11 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2020-02-29</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5767,29 +5703,29 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM SOJA Exceto Semeadura Exportacoes KG</t>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Exportacoes KG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>12019000</t>
+          <t>09011110</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5822,29 +5758,29 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Comexstat Comex NCM SOJA Exceto Semeadura Importacoes KG</t>
+          <t>Comexstat Comex NCM CAFE NAO Torrado Importacoes KG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>12019000</t>
+          <t>09011110</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5863,49 +5799,53 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5914,49 +5854,53 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DIF CDI</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Comexstat Comex NCM Carne Bovina Congelada Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>02023000</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5965,49 +5909,53 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DIF Juros Credito Total</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6016,49 +5964,53 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DIF Selic META</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Comexstat Comex NCM Celulose NAO Coniferas Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>47032900</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6067,49 +6019,53 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DIF Selic OVER</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>Comexstat Comex NCM FUEL OIL Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6118,49 +6074,53 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Juros Credito Total</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>Comexstat Comex NCM FUEL OIL Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>27101922</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6169,11 +6129,11 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6183,35 +6143,39 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Selic META</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Comexstat Comex NCM Milho EM GRAO Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6220,49 +6184,53 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Selic OVER</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Comexstat Comex NCM Milho EM GRAO Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>10059010</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6271,49 +6239,53 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.json</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Reservas Internacionais</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6322,75 +6294,2143 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.json</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.csv</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Minerio Ferro NAO Aglomerado Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>26011100</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>66</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>80</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Oleos Brutos Petroleo Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>27090010</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>80</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>80</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM Residuos OLEO SOJA Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>23040090</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2020-02-29</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Exportacoes KG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>80</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Comexstat Comex NCM SOJA Exceto Semeadura Importacoes KG</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12019000</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>76</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.json</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>comexstat_fuel_oil_exp_fob</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Comexstat FUEL OIL EXP FOB</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>80</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_fuel_oil_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_fuel_oil_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>comexstat_fuel_oil_exp_kg</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Comexstat FUEL OIL EXP KG</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>80</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_fuel_oil_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_fuel_oil_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>comexstat_fuel_oil_imp_fob</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Comexstat FUEL OIL IMP FOB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>43</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_fuel_oil_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_fuel_oil_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>comexstat_fuel_oil_imp_kg</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Comexstat FUEL OIL IMP KG</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>43</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_fuel_oil_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_fuel_oil_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>comexstat_milho_em_grao_exp_fob</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Comexstat Milho EM GRAO EXP FOB</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>80</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_milho_em_grao_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_milho_em_grao_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>comexstat_milho_em_grao_exp_kg</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Comexstat Milho EM GRAO EXP KG</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>80</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_milho_em_grao_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_milho_em_grao_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>comexstat_milho_em_grao_imp_fob</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Comexstat Milho EM GRAO IMP FOB</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>80</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_milho_em_grao_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_milho_em_grao_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>comexstat_milho_em_grao_imp_kg</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Comexstat Milho EM GRAO IMP KG</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>80</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_milho_em_grao_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_milho_em_grao_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Comexstat Minerio Ferro NAO Aglomerado EXP FOB</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>80</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_minerio_ferro_nao_aglomerado_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Comexstat Minerio Ferro NAO Aglomerado EXP KG</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>80</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_minerio_ferro_nao_aglomerado_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Comexstat Minerio Ferro NAO Aglomerado IMP FOB</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>66</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_minerio_ferro_nao_aglomerado_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Comexstat Minerio Ferro NAO Aglomerado IMP KG</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>66</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_minerio_ferro_nao_aglomerado_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Comexstat Oleos Brutos Petroleo EXP FOB</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>80</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_oleos_brutos_petroleo_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Comexstat Oleos Brutos Petroleo EXP KG</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>80</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_oleos_brutos_petroleo_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Comexstat Oleos Brutos Petroleo IMP FOB</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>80</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_oleos_brutos_petroleo_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Comexstat Oleos Brutos Petroleo IMP KG</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>80</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_oleos_brutos_petroleo_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Comexstat Residuos OLEO SOJA EXP FOB</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>80</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_residuos_oleo_soja_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Comexstat Residuos OLEO SOJA EXP KG</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>80</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_residuos_oleo_soja_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Comexstat Residuos OLEO SOJA IMP FOB</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2020-02-29</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_residuos_oleo_soja_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Comexstat Residuos OLEO SOJA IMP KG</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>5</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2020-02-29</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_residuos_oleo_soja_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Comexstat SOJA Exceto Semeadura EXP FOB</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>80</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_soja_exceto_semeadura_exp_fob.json</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Comexstat SOJA Exceto Semeadura EXP KG</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>80</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_soja_exceto_semeadura_exp_kg.json</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Comexstat SOJA Exceto Semeadura IMP FOB</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>76</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_soja_exceto_semeadura_imp_fob.json</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_fob.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Comexstat SOJA Exceto Semeadura IMP KG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>76</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/comexstat_soja_exceto_semeadura_imp_kg.json</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_kg.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>61</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_cdi.json</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DIF CDI</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>60</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_cdi.json</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DIF Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>58</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DIF Selic META</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>60</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>DIF Selic OVER</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>60</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2021-10-31</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_dif_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Juros Credito Total</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>59</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_juros_credito_total.json</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Selic META</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>61</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_meta.json</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Selic OVER</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>61</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_selic_over.json</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Reservas Internacionais</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>59</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>data/final/dashboard/bcb_sgs_reservas_internacionais.json</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>VAR PCT Reservas Internacionais</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
         <is>
           <t>bcb_sgs</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
         <v>58</v>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>2021-10-31</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t>data/final/dashboard/bcb_sgs_var_pct_reservas_internacionais.json</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K154" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
